--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261015.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261015.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>546,955,426</t>
+          <t>11,570,539</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>11,570,539</t>
+          <t>546,955,426</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>276,135,649</t>
+          <t>2,195,318</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,195,318</t>
+          <t>1,877,575</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,877,575</t>
+          <t>276,135,649</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>70,522,546</t>
+          <t>1,287,220</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,287,220</t>
+          <t>70,522,546</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
